--- a/VerveStacks_MYS_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_MYS_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8165A8B-AB20-4628-9165-7151C8C90A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EA3BFE5-E176-48E5-8EE9-FD89A9A5285B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -3351,7 +3351,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA61ABA2-6FAB-4E0B-817A-EE4A35DC0B37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05B37B68-6ED9-4F4C-B71B-92381DB34B56}">
   <dimension ref="B2:AF487"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -13228,7 +13228,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4312C3-223D-4379-B446-E6AEDDA0FEBD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC9D40EC-A9EE-4632-84D0-0EFEE8042A1C}">
   <dimension ref="B9:L60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
